--- a/data/trans_orig/P6710-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6710-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede decidir cuándo hace un descanso en 2012</t>
+          <t>Población según si puede decidir cuándo hace un descanso en 2012 (tasa de respuesta: 98,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12938</t>
+          <t>12921</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30053</t>
+          <t>30465</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23346</t>
+          <t>23327</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25831</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48520</t>
+          <t>46858</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>27,46%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15100</t>
+          <t>15284</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>963</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8840</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>20956</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>10854</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27569</t>
+          <t>27563</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7733</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21842</t>
+          <t>20477</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22143</t>
+          <t>23662</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42804</t>
+          <t>43644</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21912</t>
+          <t>21775</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13059</t>
+          <t>12857</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29859</t>
+          <t>28814</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22769</t>
+          <t>24582</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45001</t>
+          <t>45618</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13382</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30137</t>
+          <t>29898</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27178</t>
+          <t>26209</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44439</t>
+          <t>45349</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>44348</t>
+          <t>43982</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69399</t>
+          <t>69473</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29174</t>
+          <t>30543</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52696</t>
+          <t>56351</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29415</t>
+          <t>29414</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55463</t>
+          <t>53910</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65380</t>
+          <t>64059</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100581</t>
+          <t>98018</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14734</t>
+          <t>14423</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33474</t>
+          <t>34057</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18245</t>
+          <t>18385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40222</t>
+          <t>40202</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38022</t>
+          <t>37487</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69965</t>
+          <t>66990</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80734</t>
+          <t>82505</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>115543</t>
+          <t>116840</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39782</t>
+          <t>39223</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65196</t>
+          <t>65067</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>128842</t>
+          <t>127189</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>171031</t>
+          <t>172342</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61422</t>
+          <t>61994</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93677</t>
+          <t>93492</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40280</t>
+          <t>41991</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66752</t>
+          <t>66764</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108300</t>
+          <t>108202</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148058</t>
+          <t>149384</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>122693</t>
+          <t>123003</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161506</t>
+          <t>161107</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83162</t>
+          <t>82893</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>115751</t>
+          <t>114208</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>216561</t>
+          <t>213980</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>267199</t>
+          <t>266858</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,93%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22761</t>
+          <t>23047</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44973</t>
+          <t>43618</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21535</t>
+          <t>21517</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42873</t>
+          <t>43996</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49391</t>
+          <t>49414</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79846</t>
+          <t>80427</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33209</t>
+          <t>34759</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60979</t>
+          <t>61320</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23281</t>
+          <t>24644</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46392</t>
+          <t>47716</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64080</t>
+          <t>63064</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>100508</t>
+          <t>100152</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59684</t>
+          <t>59565</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92050</t>
+          <t>91410</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45572</t>
+          <t>45535</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>73670</t>
+          <t>72433</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>114076</t>
+          <t>114722</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>156714</t>
+          <t>156845</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87706</t>
+          <t>91480</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124496</t>
+          <t>126068</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48457</t>
+          <t>48913</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75831</t>
+          <t>76160</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>148282</t>
+          <t>145285</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>192484</t>
+          <t>192129</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>140034</t>
+          <t>141143</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>181216</t>
+          <t>181740</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82466</t>
+          <t>82868</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>114851</t>
+          <t>114972</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>232159</t>
+          <t>232832</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>285033</t>
+          <t>283802</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23646</t>
+          <t>23642</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47046</t>
+          <t>45969</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22257</t>
+          <t>21334</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44225</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50317</t>
+          <t>50362</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>83010</t>
+          <t>82973</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20945</t>
+          <t>20645</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42240</t>
+          <t>40863</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34868</t>
+          <t>34386</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>38328</t>
+          <t>38825</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>67366</t>
+          <t>70125</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56333</t>
+          <t>56369</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>88423</t>
+          <t>88904</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>28449</t>
+          <t>27353</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53333</t>
+          <t>54843</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>93917</t>
+          <t>91456</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>134654</t>
+          <t>134399</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59716</t>
+          <t>57635</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>90684</t>
+          <t>90791</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28864</t>
+          <t>29838</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52853</t>
+          <t>52977</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>94929</t>
+          <t>93669</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>133681</t>
+          <t>135612</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>136888</t>
+          <t>138357</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>179307</t>
+          <t>178806</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>74166</t>
+          <t>74746</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>106470</t>
+          <t>105455</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>224073</t>
+          <t>225141</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>274157</t>
+          <t>275402</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19983</t>
+          <t>19459</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10226</t>
+          <t>10104</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24441</t>
+          <t>23065</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>13147</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>14240</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21951</t>
+          <t>22097</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>42061</t>
+          <t>42077</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>6379</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21118</t>
+          <t>20698</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>32686</t>
+          <t>32049</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>58529</t>
+          <t>56632</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21459</t>
+          <t>20830</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41420</t>
+          <t>41370</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21767</t>
+          <t>21373</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>33755</t>
+          <t>33252</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>58653</t>
+          <t>57847</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>65918</t>
+          <t>66845</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>90648</t>
+          <t>92286</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>27972</t>
+          <t>28254</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>45532</t>
+          <t>45976</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>100895</t>
+          <t>100518</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>131390</t>
+          <t>132032</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,4%</t>
         </is>
       </c>
     </row>
@@ -4141,97 +4141,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4254,97 +4254,97 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>114556</t>
+          <t>114738</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>164220</t>
+          <t>162582</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>100649</t>
+          <t>103443</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>143729</t>
+          <t>145822</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>232853</t>
+          <t>231854</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>298284</t>
+          <t>293419</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>92123</t>
+          <t>90642</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>135760</t>
+          <t>135581</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>72394</t>
+          <t>74131</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>112893</t>
+          <t>112108</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>175147</t>
+          <t>176266</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>231292</t>
+          <t>234070</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>263089</t>
+          <t>265133</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>323334</t>
+          <t>325211</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>153510</t>
+          <t>152244</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>202693</t>
+          <t>203388</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>432261</t>
+          <t>433235</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>511929</t>
+          <t>515575</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>272158</t>
+          <t>269276</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>335218</t>
+          <t>333028</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>164464</t>
+          <t>162389</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>214331</t>
+          <t>211832</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>451391</t>
+          <t>449582</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>533910</t>
+          <t>533129</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>525311</t>
+          <t>529498</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>597471</t>
+          <t>602581</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>333239</t>
+          <t>333069</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>391467</t>
+          <t>393339</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>879634</t>
+          <t>876157</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>977402</t>
+          <t>973936</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede decidir cuándo hace un descanso en 2016</t>
+          <t>Población según si puede decidir cuándo hace un descanso en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20345</t>
+          <t>20436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20109</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17031</t>
+          <t>17938</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35767</t>
+          <t>35706</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9244</t>
+          <t>9678</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>24073</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14838</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31272</t>
+          <t>30830</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27415</t>
+          <t>26698</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49073</t>
+          <t>49726</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17179</t>
+          <t>16412</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33514</t>
+          <t>33608</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14984</t>
+          <t>14080</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30503</t>
+          <t>30173</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35414</t>
+          <t>36100</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>60887</t>
+          <t>60402</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>10281</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24989</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12589</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27713</t>
+          <t>28539</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26127</t>
+          <t>26307</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47716</t>
+          <t>46654</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16186</t>
+          <t>15746</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>9690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22995</t>
+          <t>24023</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16897</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34247</t>
+          <t>35184</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>35970</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63395</t>
+          <t>62690</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31246</t>
+          <t>32689</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53858</t>
+          <t>55850</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71106</t>
+          <t>73265</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106935</t>
+          <t>106940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55865</t>
+          <t>56309</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85428</t>
+          <t>87103</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42604</t>
+          <t>41615</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67604</t>
+          <t>67829</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104082</t>
+          <t>106117</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146552</t>
+          <t>147160</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>65109</t>
+          <t>66789</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>96596</t>
+          <t>97194</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57892</t>
+          <t>58733</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87137</t>
+          <t>86297</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>131061</t>
+          <t>132381</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>173972</t>
+          <t>174939</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55652</t>
+          <t>55768</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85483</t>
+          <t>86643</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45017</t>
+          <t>44227</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70598</t>
+          <t>69622</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108278</t>
+          <t>107084</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>147689</t>
+          <t>145079</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60745</t>
+          <t>63221</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92488</t>
+          <t>94158</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36898</t>
+          <t>37686</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61979</t>
+          <t>62474</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>107420</t>
+          <t>104189</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>144916</t>
+          <t>144968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41064</t>
+          <t>41228</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69503</t>
+          <t>69599</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36562</t>
+          <t>36678</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62289</t>
+          <t>60917</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84856</t>
+          <t>82613</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121010</t>
+          <t>120656</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51004</t>
+          <t>50881</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82835</t>
+          <t>81603</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44275</t>
+          <t>44421</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72515</t>
+          <t>70234</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>101649</t>
+          <t>101835</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>143358</t>
+          <t>142403</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106823</t>
+          <t>106027</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>146787</t>
+          <t>144867</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>64991</t>
+          <t>63762</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>93868</t>
+          <t>94357</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>179365</t>
+          <t>178922</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>228067</t>
+          <t>227598</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81388</t>
+          <t>83467</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>119196</t>
+          <t>119050</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>35376</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60642</t>
+          <t>60535</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>124469</t>
+          <t>127019</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169703</t>
+          <t>170824</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>97228</t>
+          <t>96643</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>134914</t>
+          <t>133251</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71260</t>
+          <t>70264</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>103693</t>
+          <t>101468</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>177931</t>
+          <t>176568</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>227031</t>
+          <t>226902</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36023</t>
+          <t>35935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64531</t>
+          <t>64682</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27949</t>
+          <t>27178</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51050</t>
+          <t>51644</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>68491</t>
+          <t>69764</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106367</t>
+          <t>106181</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36995</t>
+          <t>36591</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63579</t>
+          <t>64528</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25724</t>
+          <t>25817</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48120</t>
+          <t>48363</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>70583</t>
+          <t>68737</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>105640</t>
+          <t>104527</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>77622</t>
+          <t>79215</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>113406</t>
+          <t>114560</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49647</t>
+          <t>50621</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>76676</t>
+          <t>78671</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>134548</t>
+          <t>138816</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>180779</t>
+          <t>182365</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>63245</t>
+          <t>62386</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>97208</t>
+          <t>96523</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34045</t>
+          <t>33915</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60192</t>
+          <t>59672</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>103172</t>
+          <t>104934</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>147028</t>
+          <t>145825</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76904</t>
+          <t>78373</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>114125</t>
+          <t>114066</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45140</t>
+          <t>45395</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>74119</t>
+          <t>72142</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>134601</t>
+          <t>131808</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>179850</t>
+          <t>174131</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10571</t>
+          <t>10184</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27028</t>
+          <t>26508</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23060</t>
+          <t>24507</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>22132</t>
+          <t>22095</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>44915</t>
+          <t>45848</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>14741</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34924</t>
+          <t>34413</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12508</t>
+          <t>12023</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29567</t>
+          <t>28943</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31570</t>
+          <t>31170</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>57080</t>
+          <t>57677</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>25616</t>
+          <t>27235</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>48235</t>
+          <t>49159</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18320</t>
+          <t>18880</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>38036</t>
+          <t>38662</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>49859</t>
+          <t>49794</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>80345</t>
+          <t>80133</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,5%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22569</t>
+          <t>22209</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>45082</t>
+          <t>44229</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12913</t>
+          <t>12504</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>29220</t>
+          <t>28714</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>39266</t>
+          <t>38962</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>66777</t>
+          <t>67073</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43231</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>68082</t>
+          <t>68489</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16069</t>
+          <t>15809</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>34461</t>
+          <t>35026</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>63542</t>
+          <t>64107</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>95966</t>
+          <t>96944</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,69%</t>
         </is>
       </c>
     </row>
@@ -9832,97 +9832,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9945,97 +9945,97 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>62,38%</t>
         </is>
       </c>
     </row>
@@ -10171,97 +10171,97 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>4140</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>19,91%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>79,77%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>1033</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>4156</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>5165</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>80,07%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>1034</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>5124</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>9,96%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,76%</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>864</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9342</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,05%</t>
         </is>
       </c>
     </row>
@@ -10514,97 +10514,97 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10627,97 +10627,97 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10740,97 +10740,97 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10853,97 +10853,97 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
           <t>795</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10966,97 +10966,97 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>156014</t>
+          <t>156755</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>209125</t>
+          <t>207443</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>135678</t>
+          <t>134522</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>179859</t>
+          <t>182724</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>304203</t>
+          <t>307370</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>372554</t>
+          <t>377543</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>199302</t>
+          <t>197332</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>253631</t>
+          <t>254758</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>161851</t>
+          <t>166869</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>213099</t>
+          <t>215976</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>375103</t>
+          <t>379011</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>447793</t>
+          <t>454149</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>330543</t>
+          <t>332339</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>396966</t>
+          <t>397845</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>237795</t>
+          <t>236071</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>291371</t>
+          <t>294530</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>587163</t>
+          <t>588022</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>674244</t>
+          <t>675725</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>268041</t>
+          <t>268688</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>330344</t>
+          <t>329628</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>166721</t>
+          <t>166734</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>216769</t>
+          <t>217675</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>451734</t>
+          <t>449150</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>530621</t>
+          <t>530009</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>324521</t>
+          <t>321071</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>390279</t>
+          <t>389656</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>211355</t>
+          <t>208464</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>263673</t>
+          <t>262282</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>548870</t>
+          <t>545625</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>635214</t>
+          <t>635364</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">

--- a/data/trans_orig/P6710-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6710-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12921</t>
+          <t>12757</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30465</t>
+          <t>29986</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>8916</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23327</t>
+          <t>23205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>25999</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46858</t>
+          <t>48525</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15284</t>
+          <t>15979</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>8725</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20956</t>
+          <t>20615</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>11281</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27563</t>
+          <t>27025</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,82 +972,82 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>13,62%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>32,62%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>13626</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>7743</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>21247</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>15,52%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>24,2%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>32039</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>22360</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>43839</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>18,77%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>13,1%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>33,27%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>13626</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>7924</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>20477</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>9,03%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>23,32%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>32039</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>23662</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>43644</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>13,87%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21775</t>
+          <t>22063</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28814</t>
+          <t>29520</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24582</t>
+          <t>23246</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45618</t>
+          <t>45621</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14042</t>
+          <t>14633</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29898</t>
+          <t>31088</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26209</t>
+          <t>25338</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45349</t>
+          <t>43967</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43982</t>
+          <t>44585</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69473</t>
+          <t>68089</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>39,9%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30543</t>
+          <t>29708</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56351</t>
+          <t>54360</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29414</t>
+          <t>29110</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53910</t>
+          <t>55288</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64059</t>
+          <t>64723</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98018</t>
+          <t>100515</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14423</t>
+          <t>13970</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34057</t>
+          <t>34945</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18385</t>
+          <t>18697</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40202</t>
+          <t>40815</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37487</t>
+          <t>37483</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66990</t>
+          <t>66406</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82505</t>
+          <t>81486</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116840</t>
+          <t>115707</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39223</t>
+          <t>39176</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65067</t>
+          <t>65878</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>127189</t>
+          <t>127958</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>172342</t>
+          <t>171945</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61994</t>
+          <t>61384</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93492</t>
+          <t>93479</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41991</t>
+          <t>40075</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66764</t>
+          <t>67091</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108202</t>
+          <t>109855</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149384</t>
+          <t>151320</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>123003</t>
+          <t>122734</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161107</t>
+          <t>164158</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82893</t>
+          <t>81494</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114208</t>
+          <t>114886</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>213980</t>
+          <t>214420</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>266858</t>
+          <t>265169</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23047</t>
+          <t>23492</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43618</t>
+          <t>45780</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>21318</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43996</t>
+          <t>41778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49414</t>
+          <t>48008</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80427</t>
+          <t>78600</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34759</t>
+          <t>34347</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61320</t>
+          <t>63667</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24644</t>
+          <t>24629</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47716</t>
+          <t>48446</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63064</t>
+          <t>63708</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>100152</t>
+          <t>100126</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59565</t>
+          <t>59604</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91410</t>
+          <t>90228</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45535</t>
+          <t>44946</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72433</t>
+          <t>72184</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>114722</t>
+          <t>112985</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>156845</t>
+          <t>155682</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91480</t>
+          <t>89797</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>126068</t>
+          <t>123880</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48913</t>
+          <t>48751</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>76160</t>
+          <t>76669</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>145285</t>
+          <t>146674</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>192129</t>
+          <t>194018</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>141143</t>
+          <t>141811</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>181740</t>
+          <t>182004</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82868</t>
+          <t>81832</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>114972</t>
+          <t>114787</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>232832</t>
+          <t>232741</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>283802</t>
+          <t>285956</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23642</t>
+          <t>22937</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45969</t>
+          <t>46643</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21334</t>
+          <t>22891</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>44269</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50362</t>
+          <t>49624</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>82973</t>
+          <t>84092</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20645</t>
+          <t>19491</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40863</t>
+          <t>42012</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14282</t>
+          <t>13713</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34386</t>
+          <t>34493</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>38825</t>
+          <t>39867</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>70125</t>
+          <t>69160</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56369</t>
+          <t>56041</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>88904</t>
+          <t>88575</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27353</t>
+          <t>28740</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>54843</t>
+          <t>54243</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>91456</t>
+          <t>90366</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>134399</t>
+          <t>131630</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57635</t>
+          <t>59220</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>90791</t>
+          <t>90918</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29838</t>
+          <t>27311</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52977</t>
+          <t>51619</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>93669</t>
+          <t>93763</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>135612</t>
+          <t>135483</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>138357</t>
+          <t>139507</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>178806</t>
+          <t>180047</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>74746</t>
+          <t>73705</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>105455</t>
+          <t>106113</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>225141</t>
+          <t>222253</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>275402</t>
+          <t>274723</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,42%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19459</t>
+          <t>20188</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8640</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23065</t>
+          <t>25563</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13147</t>
+          <t>13079</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7275</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14240</t>
+          <t>15691</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22097</t>
+          <t>21403</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>42077</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6379</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>20698</t>
+          <t>20895</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>32049</t>
+          <t>33008</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>56632</t>
+          <t>56485</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20830</t>
+          <t>20313</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41370</t>
+          <t>41646</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>7758</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>22183</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>33252</t>
+          <t>33341</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>57847</t>
+          <t>57157</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>66845</t>
+          <t>65825</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>92286</t>
+          <t>91859</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28254</t>
+          <t>28988</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>45976</t>
+          <t>46117</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>100518</t>
+          <t>100379</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>132032</t>
+          <t>131091</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>57,99%</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,96%</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>997</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>114738</t>
+          <t>117612</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>162582</t>
+          <t>163242</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>103443</t>
+          <t>102976</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>145822</t>
+          <t>142747</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>231854</t>
+          <t>230016</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>293419</t>
+          <t>295208</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>90642</t>
+          <t>92345</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>135581</t>
+          <t>134757</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>74131</t>
+          <t>74576</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>112108</t>
+          <t>113999</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>176266</t>
+          <t>175011</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>234070</t>
+          <t>233128</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>265133</t>
+          <t>261695</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>325211</t>
+          <t>323087</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>152244</t>
+          <t>154541</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>203388</t>
+          <t>202533</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>433235</t>
+          <t>429307</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>515575</t>
+          <t>514697</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>269276</t>
+          <t>270920</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>333028</t>
+          <t>334641</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>162389</t>
+          <t>162682</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>211832</t>
+          <t>216078</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>449582</t>
+          <t>452735</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>533129</t>
+          <t>531013</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>529498</t>
+          <t>525793</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>602581</t>
+          <t>599413</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>333069</t>
+          <t>331589</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>393339</t>
+          <t>392868</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>876157</t>
+          <t>878083</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>973936</t>
+          <t>978907</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20436</t>
+          <t>20772</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7211</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>20433</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17938</t>
+          <t>17821</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35706</t>
+          <t>36684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24073</t>
+          <t>23052</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14202</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30830</t>
+          <t>31063</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26698</t>
+          <t>26920</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49726</t>
+          <t>48564</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16412</t>
+          <t>16760</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33608</t>
+          <t>33562</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14080</t>
+          <t>14645</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30173</t>
+          <t>30136</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36100</t>
+          <t>36349</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>60402</t>
+          <t>59043</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10281</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24989</t>
+          <t>24992</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12589</t>
+          <t>12926</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28539</t>
+          <t>28339</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26307</t>
+          <t>26980</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46654</t>
+          <t>47692</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15746</t>
+          <t>15822</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>9582</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24023</t>
+          <t>23787</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>16240</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35184</t>
+          <t>34517</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35970</t>
+          <t>35955</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62690</t>
+          <t>61179</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32689</t>
+          <t>32957</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55850</t>
+          <t>55095</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73265</t>
+          <t>73119</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106940</t>
+          <t>109297</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56309</t>
+          <t>56351</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87103</t>
+          <t>88376</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41615</t>
+          <t>42580</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67829</t>
+          <t>67551</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>106117</t>
+          <t>105328</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>147160</t>
+          <t>147399</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66789</t>
+          <t>64904</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>97194</t>
+          <t>95554</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58733</t>
+          <t>58166</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86297</t>
+          <t>85411</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>132381</t>
+          <t>129362</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>174939</t>
+          <t>172903</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55768</t>
+          <t>55743</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86643</t>
+          <t>86886</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44227</t>
+          <t>44937</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69622</t>
+          <t>70570</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107084</t>
+          <t>108587</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145079</t>
+          <t>149463</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63221</t>
+          <t>62224</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94158</t>
+          <t>92587</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37686</t>
+          <t>38299</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62474</t>
+          <t>62478</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>104189</t>
+          <t>106377</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>144968</t>
+          <t>146462</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41228</t>
+          <t>41391</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69599</t>
+          <t>68311</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36678</t>
+          <t>36726</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60917</t>
+          <t>61822</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82613</t>
+          <t>85184</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120656</t>
+          <t>123712</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50881</t>
+          <t>51301</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81603</t>
+          <t>81477</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44421</t>
+          <t>44065</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70234</t>
+          <t>70161</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>101835</t>
+          <t>101160</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>142403</t>
+          <t>142391</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106027</t>
+          <t>107420</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>144867</t>
+          <t>145259</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63762</t>
+          <t>65037</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>94357</t>
+          <t>94844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>178922</t>
+          <t>181378</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>227598</t>
+          <t>228274</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,38%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83467</t>
+          <t>82329</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>119050</t>
+          <t>118324</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35376</t>
+          <t>36044</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60535</t>
+          <t>62178</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>127019</t>
+          <t>123300</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>170824</t>
+          <t>169728</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>96643</t>
+          <t>95203</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>133251</t>
+          <t>134637</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70264</t>
+          <t>69878</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101468</t>
+          <t>102116</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>176568</t>
+          <t>177877</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>226902</t>
+          <t>227579</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35935</t>
+          <t>36226</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64682</t>
+          <t>64101</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,82 +8483,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>17,43%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>38432</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>27409</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>51204</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>15,81%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>11,27%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>21,06%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>87405</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>69958</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>107467</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>14,31%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>11,45%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>17,59%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>38432</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>27178</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>51644</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>15,81%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>11,18%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>21,24%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>87405</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>69764</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>106181</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>14,31%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>11,42%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36591</t>
+          <t>36166</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>64528</t>
+          <t>63982</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25817</t>
+          <t>26664</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48363</t>
+          <t>49094</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>68737</t>
+          <t>69165</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>104527</t>
+          <t>105322</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>79215</t>
+          <t>77191</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>114560</t>
+          <t>113042</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>50621</t>
+          <t>49687</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>78671</t>
+          <t>77239</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>138816</t>
+          <t>135471</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>182365</t>
+          <t>180115</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,49%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>62386</t>
+          <t>63886</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96523</t>
+          <t>96911</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33915</t>
+          <t>34736</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59672</t>
+          <t>59719</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>104934</t>
+          <t>107545</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>145825</t>
+          <t>148440</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78373</t>
+          <t>78770</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>114066</t>
+          <t>113772</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45395</t>
+          <t>45423</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>72142</t>
+          <t>73105</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>131808</t>
+          <t>133658</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>174131</t>
+          <t>174930</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>10776</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26508</t>
+          <t>27955</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24507</t>
+          <t>24129</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>22095</t>
+          <t>21560</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>45848</t>
+          <t>44394</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14741</t>
+          <t>15883</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34413</t>
+          <t>35417</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>11966</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28943</t>
+          <t>28469</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31170</t>
+          <t>32036</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>57677</t>
+          <t>57163</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>27235</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>49159</t>
+          <t>49389</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18880</t>
+          <t>18697</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>38662</t>
+          <t>38762</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>49794</t>
+          <t>51576</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>80133</t>
+          <t>81100</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22209</t>
+          <t>22476</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>44229</t>
+          <t>44635</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12504</t>
+          <t>12632</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>28714</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>38962</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>67073</t>
+          <t>65408</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>43231</t>
+          <t>42340</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>68489</t>
+          <t>68268</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>15809</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>35026</t>
+          <t>34568</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>64107</t>
+          <t>63885</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>96944</t>
+          <t>94764</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>34,89%</t>
         </is>
       </c>
     </row>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,28%</t>
         </is>
       </c>
     </row>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,99%</t>
         </is>
       </c>
     </row>
@@ -10284,7 +10284,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>856</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,79%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>156755</t>
+          <t>155977</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>207443</t>
+          <t>209313</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>134522</t>
+          <t>134300</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>182724</t>
+          <t>180331</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>307370</t>
+          <t>306972</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>377543</t>
+          <t>373003</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>197332</t>
+          <t>195696</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>254758</t>
+          <t>252340</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>166869</t>
+          <t>165494</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>215976</t>
+          <t>212940</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>379011</t>
+          <t>379810</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>454149</t>
+          <t>456150</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>332339</t>
+          <t>331834</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>397845</t>
+          <t>400174</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>236071</t>
+          <t>237273</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>294530</t>
+          <t>292631</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>588022</t>
+          <t>584437</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>675725</t>
+          <t>670724</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>268688</t>
+          <t>267259</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>329628</t>
+          <t>328269</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>166734</t>
+          <t>169858</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>217675</t>
+          <t>217528</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>449150</t>
+          <t>449467</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>530009</t>
+          <t>528774</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>321071</t>
+          <t>323428</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>389656</t>
+          <t>393283</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>208464</t>
+          <t>208440</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>262282</t>
+          <t>263212</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11703,7 +11703,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>545625</t>
+          <t>545488</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>635364</t>
+          <t>636334</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
